--- a/Data/MST/All_players.xlsx
+++ b/Data/MST/All_players.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -714,7 +714,9 @@
         <v>12909</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>428</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -759,7 +761,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22">
@@ -773,7 +775,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +833,7 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
@@ -867,7 +869,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29">
@@ -957,7 +959,7 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35">
@@ -975,7 +977,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36">
@@ -1077,7 +1079,7 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
@@ -1095,7 +1097,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
@@ -1109,7 +1111,7 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45">
@@ -1123,7 +1125,7 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46">
@@ -1185,7 +1187,7 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50">
@@ -1203,7 +1205,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51">
@@ -1253,7 +1255,7 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54">
@@ -1303,7 +1305,7 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57">
@@ -1321,7 +1323,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -1339,7 +1341,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59">
@@ -1471,7 +1473,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67">
@@ -1497,7 +1499,7 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="69">
@@ -1627,7 +1629,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1643,7 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78">
@@ -1659,7 +1661,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81">
@@ -1709,7 +1711,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82">
@@ -1723,7 +1725,7 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1761,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85">
@@ -1777,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1797,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87">
@@ -1813,7 +1815,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88">
@@ -1841,7 +1843,7 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90">
@@ -1873,7 +1875,7 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92">
@@ -1927,7 +1929,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95">
@@ -1971,7 +1973,7 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98">
@@ -1997,7 +1999,7 @@
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100">
@@ -2051,7 +2053,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103">
@@ -2069,7 +2071,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104">
@@ -2113,7 +2115,7 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107">
@@ -2161,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110">
@@ -2203,7 +2205,7 @@
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113">
@@ -2254,7 +2256,9 @@
         <v>13497</v>
       </c>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>496</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2285,7 +2289,7 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119">
@@ -2313,7 +2317,7 @@
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121">
@@ -2331,7 +2335,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122">
@@ -2461,7 +2465,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130">
@@ -2549,7 +2553,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138">
@@ -2623,7 +2627,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140">
@@ -2651,7 +2655,7 @@
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="142">
@@ -2837,7 +2841,7 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="155">
@@ -2915,7 +2919,7 @@
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="164">
@@ -3015,7 +3019,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166">
@@ -3029,7 +3033,7 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="167">
@@ -3181,7 +3185,7 @@
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177">
@@ -3195,7 +3199,7 @@
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="178">
@@ -3261,7 +3265,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182">
@@ -3275,7 +3279,7 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="183">
@@ -3289,7 +3293,7 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="184">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="188">
@@ -3381,7 +3385,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="190">
@@ -3413,7 +3417,7 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="192">
@@ -3526,9 +3530,7 @@
         <v>8480</v>
       </c>
       <c r="C198" t="inlineStr"/>
-      <c r="D198" t="n">
-        <v>494</v>
-      </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3541,7 +3543,7 @@
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="200">
@@ -3555,7 +3557,7 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="201">
@@ -3569,7 +3571,7 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202">
@@ -3641,7 +3643,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="206">
@@ -3659,7 +3661,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="207">
@@ -3697,7 +3699,7 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="210">
@@ -3733,7 +3735,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="212">
@@ -3777,7 +3779,7 @@
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215">
@@ -3790,7 +3792,9 @@
         <v>15651</v>
       </c>
       <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3807,7 +3811,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="217">
@@ -3821,7 +3825,7 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="218">
@@ -3835,7 +3839,7 @@
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="219">
@@ -3849,7 +3853,7 @@
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="220">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
     </row>
     <row r="221">
@@ -3881,7 +3885,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222">
@@ -3906,7 +3910,9 @@
         <v>12920</v>
       </c>
       <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="n">
+        <v>375</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3931,7 +3937,7 @@
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="226">
@@ -3945,7 +3951,7 @@
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="227">
@@ -3991,7 +3997,7 @@
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="230">
@@ -4009,7 +4015,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="231">
@@ -4027,7 +4033,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
